--- a/assets/pricing_models/C.xlsx
+++ b/assets/pricing_models/C.xlsx
@@ -40,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12.0"/>
       <color indexed="8"/>
@@ -61,7 +61,12 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="30.0"/>
+      <sz val="26.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="26.0"/>
       <b val="true"/>
     </font>
     <font>
@@ -92,12 +97,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDE59"/>
+        <fgColor rgb="FFED59"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3C2"/>
+        <fgColor rgb="FFF3C3"/>
       </patternFill>
     </fill>
     <fill>
@@ -106,7 +111,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -318,11 +323,63 @@
         <color rgb="1800AD"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="545454"/>
+      </left>
+      <right style="thick"/>
+      <top style="thick">
+        <color rgb="1800AD"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="545454"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="545454"/>
+      </left>
+      <right style="thick">
+        <color rgb="1800AD"/>
+      </right>
+      <top style="thick">
+        <color rgb="1800AD"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="545454"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="545454"/>
+      </left>
+      <right style="thick"/>
+      <top style="medium">
+        <color rgb="545454"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="1800AD"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="545454"/>
+      </left>
+      <right style="thick">
+        <color rgb="1800AD"/>
+      </right>
+      <top style="medium">
+        <color rgb="545454"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="1800AD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
       <alignment wrapText="true" horizontal="center"/>
@@ -330,19 +387,28 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
       <alignment readingOrder="2" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
       <alignment readingOrder="2" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="24" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
       <alignment readingOrder="2" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="24" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="26" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
       <alignment readingOrder="2" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="28" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
       <alignment readingOrder="2" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="6" borderId="24" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment readingOrder="2" wrapText="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="24" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment readingOrder="2" wrapText="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="26" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment readingOrder="2" wrapText="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="6" borderId="28" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
       <alignment readingOrder="2" wrapText="true" horizontal="center"/>
     </xf>
   </cellXfs>
@@ -410,322 +476,322 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" ht="54.0" customHeight="true">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="7" t="n">
         <v>210.0</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="7" t="n">
         <v>185.0</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="2" t="n">
         <v>22.0</v>
       </c>
     </row>
     <row r="4" ht="54.0" customHeight="true">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="8" t="n">
         <v>240.0</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="8" t="n">
         <v>205.0</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="2" t="n">
         <v>24.0</v>
       </c>
     </row>
     <row r="5" ht="54.0" customHeight="true">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="7" t="n">
         <v>150.0</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="7" t="n">
         <v>270.0</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>210.0</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="9" t="n">
         <v>230.0</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="2" t="n">
         <v>26.0</v>
       </c>
     </row>
     <row r="6" ht="54.0" customHeight="true">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="8" t="n">
         <v>170.0</v>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="8" t="n">
         <v>305.0</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>240.0</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="10" t="n">
         <v>255.0</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="2" t="n">
         <v>28.0</v>
       </c>
     </row>
     <row r="7" ht="54.0" customHeight="true">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="7" t="n">
         <v>195.0</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <v>340.0</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>270.0</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="9" t="n">
         <v>280.0</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="2" t="n">
         <v>30.0</v>
       </c>
     </row>
     <row r="8" ht="54.0" customHeight="true">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="8" t="n">
         <v>220.0</v>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="n">
         <v>375.0</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>300.0</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="10" t="n">
         <v>305.0</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="2" t="n">
         <v>32.0</v>
       </c>
     </row>
     <row r="9" ht="54.0" customHeight="true">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="7" t="n">
         <v>245.0</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="7" t="n">
         <v>410.0</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <v>330.0</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="9" t="n">
         <v>330.0</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="2" t="n">
         <v>34.0</v>
       </c>
     </row>
     <row r="10" ht="54.0" customHeight="true">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="8" t="n">
         <v>270.0</v>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="8" t="n">
         <v>445.0</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="8" t="n">
         <v>360.0</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="10" t="n">
         <v>355.0</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="2" t="n">
         <v>36.0</v>
       </c>
     </row>
     <row r="11" ht="54.0" customHeight="true">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="7" t="n">
         <v>295.0</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="7" t="n">
         <v>480.0</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <v>390.0</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="9" t="n">
         <v>380.0</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="2" t="n">
         <v>38.0</v>
       </c>
     </row>
     <row r="12" ht="54.0" customHeight="true">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="8" t="n">
         <v>320.0</v>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="8" t="n">
         <v>515.0</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="8" t="n">
         <v>420.0</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="10" t="n">
         <v>405.0</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="2" t="n">
         <v>40.0</v>
       </c>
     </row>
     <row r="13" ht="54.0" customHeight="true">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="7" t="n">
         <v>345.0</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="7" t="n">
         <v>550.0</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="7" t="n">
         <v>450.0</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="9" t="n">
         <v>430.0</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="2" t="n">
         <v>42.0</v>
       </c>
     </row>
     <row r="14" ht="54.0" customHeight="true">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="8" t="n">
         <v>370.0</v>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="8" t="n">
         <v>585.0</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="8" t="n">
         <v>500.0</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="10" t="n">
         <v>455.0</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="2" t="n">
         <v>44.0</v>
       </c>
     </row>
     <row r="15" ht="54.0" customHeight="true">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="7" t="n">
         <v>400.0</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="7" t="n">
         <v>625.0</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="7" t="n">
         <v>550.0</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="9" t="n">
         <v>480.0</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="2" t="n">
         <v>46.0</v>
       </c>
     </row>
     <row r="16" ht="54.0" customHeight="true">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="8" t="n">
         <v>435.0</v>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="8" t="n">
         <v>680.0</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="8" t="n">
         <v>600.0</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="10" t="n">
         <v>520.0</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="2" t="n">
         <v>48.0</v>
       </c>
     </row>
     <row r="17" ht="54.0" customHeight="true">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="7" t="n">
         <v>475.0</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="7" t="n">
         <v>735.0</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="7" t="n">
         <v>650.0</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="9" t="n">
         <v>560.0</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="2" t="n">
         <v>50.0</v>
       </c>
     </row>
     <row r="18" ht="54.0" customHeight="true">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="8" t="n">
         <v>515.0</v>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="8" t="n">
         <v>790.0</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="8" t="n">
         <v>700.0</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="10" t="n">
         <v>600.0</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="2" t="n">
         <v>52.0</v>
       </c>
     </row>
     <row r="19" ht="54.0" customHeight="true">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="7" t="n">
         <v>555.0</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="7" t="n">
         <v>845.0</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="7" t="n">
         <v>750.0</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="9" t="n">
         <v>645.0</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="2" t="n">
         <v>54.0</v>
       </c>
     </row>
     <row r="20" ht="54.0" customHeight="true">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="8" t="n">
         <v>595.0</v>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="8" t="n">
         <v>900.0</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="8" t="n">
         <v>800.0</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="10" t="n">
         <v>690.0</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="2" t="n">
         <v>56.0</v>
       </c>
     </row>
